--- a/data/trans_bre/IQ26A_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>141,66%</t>
+          <t>126,76%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 11,64</t>
+          <t>-4,0; 11,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 10,28</t>
+          <t>-4,96; 10,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 6,73</t>
+          <t>-10,85; 7,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 28,65</t>
+          <t>-2,13; 30,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 147,33</t>
+          <t>-27,68; 153,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 181,99</t>
+          <t>-43,14; 200,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 74,14</t>
+          <t>-59,74; 73,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 618,73</t>
+          <t>-24,83; 564,17</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 8,35</t>
+          <t>-9,27; 7,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 8,4</t>
+          <t>-6,0; 9,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 7,59</t>
+          <t>-9,1; 7,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 25,96</t>
+          <t>-16,43; 26,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 85,61</t>
+          <t>-48,35; 73,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 168,75</t>
+          <t>-50,55; 174,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 65,81</t>
+          <t>-44,58; 61,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 290,32</t>
+          <t>-53,14; 307,19</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,04</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 8,32</t>
+          <t>-4,93; 9,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 13,85</t>
+          <t>-2,18; 14,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 2,67</t>
+          <t>-14,0; 2,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 45,34</t>
+          <t>-11,88; 39,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 188,62</t>
+          <t>-54,57; 203,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 273,83</t>
+          <t>-22,38; 310,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-75,34; 35,92</t>
+          <t>-77,71; 30,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-67,23; 832,24</t>
+          <t>-64,91; 612,93</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 7,71</t>
+          <t>-3,15; 7,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,97</t>
+          <t>-6,32; 3,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 4,57</t>
+          <t>-6,27; 5,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 27,36</t>
+          <t>-9,74; 20,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 88,59</t>
+          <t>-23,35; 89,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 42,48</t>
+          <t>-44,95; 39,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 39,15</t>
+          <t>-33,97; 41,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 305,17</t>
+          <t>-49,72; 201,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-9,84</t>
+          <t>-9,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-30,42%</t>
+          <t>-27,69%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 9,44</t>
+          <t>-5,15; 9,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -1,04</t>
+          <t>-12,66; -0,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 3,18</t>
+          <t>-10,14; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 11,51</t>
+          <t>-27,6; 11,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 128,68</t>
+          <t>-40,6; 120,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,05; -6,84</t>
+          <t>-71,04; -0,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 27,07</t>
+          <t>-53,87; 32,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 50,8</t>
+          <t>-67,05; 51,88</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 6,7</t>
+          <t>-13,65; 6,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 4,68</t>
+          <t>-12,47; 4,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 24,28</t>
+          <t>-0,29; 24,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 36,68</t>
+          <t>-14,85; 33,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 44,62</t>
+          <t>-50,14; 43,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,01; 79,84</t>
+          <t>-82,72; 84,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 295,67</t>
+          <t>-7,76; 294,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,24; 774,94</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,49</t>
+          <t>-1,06; 4,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,03</t>
+          <t>-3,45; 2,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,63</t>
+          <t>-3,63; 2,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 14,55</t>
+          <t>-2,53; 13,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 42,8</t>
+          <t>-7,9; 44,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 21,61</t>
+          <t>-28,77; 21,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 19,96</t>
+          <t>-22,12; 19,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 99,24</t>
+          <t>-12,48; 87,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ26A_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-10,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>126,76%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.496068043708191</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.622755481792022</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.425222500094471</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>14.23675439435881</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3040483330126768</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.2880241279115143</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1027980612633308</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.267620057083393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,0; 11,66</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,96; 10,38</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,85; 7,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,13; 30,92</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-27,68; 153,2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-43,14; 200,17</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-59,74; 73,63</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-24,83; 564,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.001771215395045</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.955496577452216</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.85041337547857</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.133050704594464</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2767882993189902</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4313815357434539</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5973647800265187</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2483479677643469</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.65942412414497</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.37612154160842</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.051983357884552</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>30.92384739475008</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.531983878989793</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.001745775206526</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.736284314428834</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>5.641738398541071</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-6,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-9,27; 7,79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 9,35</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,1; 7,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-16,43; 26,86</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-48,35; 73,45</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-50,55; 174,71</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-44,58; 61,29</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-53,14; 307,19</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.3122259074129607</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.132886136961761</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.082506886662768</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6.055299699448483</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.02128403683898348</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1297212319409931</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.06703260331364815</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.2930289566914693</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,95</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,35</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-42,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>81,32%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-9.26943086102801</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.004828189394196</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.10158209766009</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-16.42724604708433</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4835135049240072</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5055402838627402</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4457899804964475</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.531377820240292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,93; 9,02</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 14,14</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-14,0; 2,28</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-11,88; 39,76</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-54,57; 203,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-22,38; 310,98</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-77,71; 30,84</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-64,91; 612,93</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.790388876490825</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.347898457107966</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.99767627405921</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>26.86005904250919</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7345084342060356</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.747144811176762</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6129266315382665</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>3.071948440429423</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-9,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29,46%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.543238043909313</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.35593080479617</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.948452716855142</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>12.34869686635998</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2112800372982174</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.7963688138742024</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4227340059282605</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.8131669214753487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 7,25</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 3,58</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,27; 5,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-9,74; 20,78</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-23,35; 89,46</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-44,95; 39,28</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-33,97; 41,01</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-49,72; 201,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.934564188792817</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.17557587521592</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-14.00362548354633</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-11.88293540795714</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5457231913824517</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2238325401896206</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7770506439847099</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6490889467941869</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.015026175589076</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>14.13956050988017</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.277720001247684</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>39.75919680055435</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.031331481580938</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.10978728202315</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3083778290221532</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>6.12932221121909</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-6,42</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,12</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-9,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-46,88%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-20,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-27,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 9,01</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,66; -0,45</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-10,14; 3,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-27,6; 11,13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-40,6; 120,24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-71,04; -0,01</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-53,87; 32,54</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-67,05; 51,88</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>1.995531081513875</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.124572429995742</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.5528264653635817</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.646344676639197</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1813514755957435</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.0959575102403042</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.03671052029051359</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.2945717974806326</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-4,16</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-4,2</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12,39</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,78</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-18,63%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-37,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.146907719995166</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.315505392590781</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.267090697032168</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-9.738075370439054</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.23353470072481</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4494613332139985</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3396851198954288</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.497232133178835</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-13,65; 6,9</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-12,47; 4,4</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 24,41</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-14,85; 33,02</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-50,14; 43,76</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-82,72; 84,4</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; 294,31</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.245242646407848</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.584502485397265</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.154849876848494</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>20.78217721395621</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.8945508989198769</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3928343202103585</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.4101221821800587</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.019099117292473</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-7,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-3,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>2.093755570836314</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-6.424788976677213</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.120188730040534</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-9.219156189431803</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1963202718185317</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.4687982226554808</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2096801143339623</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2769383684793937</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,06; 4,64</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,45; 2,05</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 2,55</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,53; 13,21</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-7,9; 44,29</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-28,77; 21,33</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-22,12; 19,13</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-12,48; 87,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.15225966191966</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-12.66485765081109</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-10.13977571923199</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-27.60075232030445</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4060327685151389</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7103527649256701</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.538668807227815</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6704662246939417</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.009294540871275</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.4455578861020962</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.589989783823834</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.12779185975945</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.202414634937761</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-5.680116845126551e-05</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3254019848321762</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.5188171401272984</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-4.161532450217692</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-4.202969546941524</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>12.39391118814542</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>5.783276498819817</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1863122172404756</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.378388911008215</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.9866396918099016</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.4292865386381157</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-13.64666181979697</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-12.47113793844787</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-0.2880761162584528</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-14.84677058844278</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.5013834348512715</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8271752107420206</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.07764755546949539</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>6.900096773574221</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4.395451480519993</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>24.40874029779038</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>33.02121934464299</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.4376455614415023</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.8439685585814469</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2.943116265481688</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.543564696859971</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.7790297453688686</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5435426527417991</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>4.750151442092207</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1275360216066265</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.07159978823354725</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.03701678087060654</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.2500459635966689</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.06335989055352</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.453888272859581</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.629710580596177</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.532043733943253</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.07901542024780489</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2877436029836707</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.2212341105378886</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1248168980419919</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4.639009775097796</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.047401982647603</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.550474943510456</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>13.20938753121176</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.4428923245867497</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.2132598545545166</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.19125999578452</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.8704734628379888</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1313,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
